--- a/results/Int All Data -0.8/Rando_5_permute.xlsx
+++ b/results/Int All Data -0.8/Rando_5_permute.xlsx
@@ -440,1487 +440,1487 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8012780895317309</v>
+        <v>0.8159229387401137</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8000138670285704</v>
+        <v>0.8190229587311599</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8023687982002428</v>
+        <v>0.8193013551676855</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7951371779963341</v>
+        <v>0.8242076084232696</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7955809933015917</v>
+        <v>0.8227026486728479</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7978767960265684</v>
+        <v>0.8245532282724075</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.801594145157521</v>
+        <v>0.8252229987132523</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7920895993062262</v>
+        <v>0.8208883204423933</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7828863269690476</v>
+        <v>0.821166716878919</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7965668193682267</v>
+        <v>0.8195111203714393</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7940612514394961</v>
+        <v>0.8111430373438375</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.795212496374863</v>
+        <v>0.8108269817180473</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7665038757288989</v>
+        <v>0.8123548185460596</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7665186578405727</v>
+        <v>0.8138449961848073</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7645846648965674</v>
+        <v>0.8144394482471231</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.751927657753288</v>
+        <v>0.8069751857618701</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7520177582434909</v>
+        <v>0.816065480531255</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.764442123105426</v>
+        <v>0.8093463068653758</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7627717444862724</v>
+        <v>0.8082703803085378</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7646680782410131</v>
+        <v>0.8070814761839064</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7634348277813598</v>
+        <v>0.8070814761839064</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.784204398593306</v>
+        <v>0.7966516405328318</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7872815415067618</v>
+        <v>0.8018215081132676</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7882297083841322</v>
+        <v>0.822011408974572</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7891778752615026</v>
+        <v>0.8203181532778276</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7854767160623832</v>
+        <v>0.825835048527561</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7851983196258576</v>
+        <v>0.825835048527561</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7853718334605064</v>
+        <v>0.8292511241443974</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7865230783958734</v>
+        <v>0.8568609411559329</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7865230783958734</v>
+        <v>0.8644219912771463</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7865230783958734</v>
+        <v>0.8810223026869655</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7838668737100848</v>
+        <v>0.8765222055473745</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.786071168124699</v>
+        <v>0.8765222055473745</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7863872237504892</v>
+        <v>0.8566860195011248</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.785920531367641</v>
+        <v>0.8469030772133045</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7946799883995619</v>
+        <v>0.8463839435295177</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8022505413068513</v>
+        <v>0.847001272669424</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8022505413068513</v>
+        <v>0.836037521222889</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7993535993738016</v>
+        <v>0.8292120571349733</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7993159401845371</v>
+        <v>0.8292120571349733</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8102501274077245</v>
+        <v>0.8260515008770719</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8105285238442501</v>
+        <v>0.8228008441289676</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8038994506685737</v>
+        <v>0.8228008441289676</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8056451476662565</v>
+        <v>0.8215890629267455</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8053667512297309</v>
+        <v>0.8244483456705307</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.806668632922156</v>
+        <v>0.8242076084232696</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.806503214053424</v>
+        <v>0.8285799458833931</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.806819269679214</v>
+        <v>0.839181887548957</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8127113490014332</v>
+        <v>0.8410930034153717</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.81656455277777</v>
+        <v>0.8373379950951546</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8162861563412444</v>
+        <v>0.8445252689640415</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8147287552898843</v>
+        <v>0.844562928153306</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8153918385849718</v>
+        <v>0.844562928153306</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.815948631458023</v>
+        <v>0.8505532029316447</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8285799458833931</v>
+        <v>0.8530749607922086</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8298980175076515</v>
+        <v>0.8519384979685155</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8327048589504982</v>
+        <v>0.851900838779251</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8356246779611385</v>
+        <v>0.8510279902804097</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8356246779611385</v>
+        <v>0.8497261085879846</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.83910128984483</v>
+        <v>0.8471828814699895</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8381154637781951</v>
+        <v>0.8487483774872663</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8344586509140977</v>
+        <v>0.8493804887388465</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8391847031892757</v>
+        <v>0.8496212259861077</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7628907052897436</v>
+        <v>0.8477625514206313</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7706939004783773</v>
+        <v>0.8470927809797866</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7738234846927714</v>
+        <v>0.848281685104418</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7655564127616081</v>
+        <v>0.8475742554743086</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7438481778583677</v>
+        <v>0.8465588651843259</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7187481522360408</v>
+        <v>0.8465588651843259</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7177098848684673</v>
+        <v>0.8456106983069556</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7160395062493137</v>
+        <v>0.8386345974619818</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7175969073006738</v>
+        <v>0.8389129938985074</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6857104845998553</v>
+        <v>0.8542867419944307</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6900356600846382</v>
+        <v>0.8582610183044777</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6689380671755467</v>
+        <v>0.858893129556058</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6729028406995177</v>
+        <v>0.8442067496529724</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6678230736092848</v>
+        <v>0.8309943574568011</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6453254035516487</v>
+        <v>0.8324993172072227</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6395543967631399</v>
+        <v>0.8289635768768355</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6393661008168172</v>
+        <v>0.8349605388009314</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6371765885138769</v>
+        <v>0.8507766943819529</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6368981920773513</v>
+        <v>0.8507766943819529</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6308487888523169</v>
+        <v>0.8476390152016421</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6190245073333352</v>
+        <v>0.8446224085550416</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6049392666383225</v>
+        <v>0.853779926737039</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6118467362505244</v>
+        <v>0.8563836901218891</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6107331505044219</v>
+        <v>0.8111113613902505</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6175424246605041</v>
+        <v>0.8103514904592029</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6175424246605041</v>
+        <v>0.8080637827001427</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5997331476887816</v>
+        <v>0.796551333346473</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5997331476887816</v>
+        <v>0.8104187138718152</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5982658471276245</v>
+        <v>0.8117730368651788</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6062788075200122</v>
+        <v>0.8068372193862468</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.605962751894222</v>
+        <v>0.8068372193862468</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6011775711723482</v>
+        <v>0.8168137369459876</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6080245045176949</v>
+        <v>0.815369313462421</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.614848560785451</v>
+        <v>0.8160390839032658</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6253375248832214</v>
+        <v>0.8180483952258003</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5704786447760017</v>
+        <v>0.8196434554664249</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5721490233951554</v>
+        <v>0.8105464735512826</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5993174887867124</v>
+        <v>0.8344118408937968</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.58939341252791</v>
+        <v>0.8156543970447039</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5927718289554819</v>
+        <v>0.7616454883587351</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5927718289554819</v>
+        <v>0.7616454883587351</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5930502253920075</v>
+        <v>0.76387265985094</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5792891352887016</v>
+        <v>0.7624954597799858</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5726829391906161</v>
+        <v>0.7625331189692504</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5717939007599413</v>
+        <v>0.7600652102297845</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5717939007599413</v>
+        <v>0.7512318426394938</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5762859029336157</v>
+        <v>0.7633774591098634</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5674525353433251</v>
+        <v>0.765958345417123</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5727420676373117</v>
+        <v>0.7653248263453833</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5702364997085813</v>
+        <v>0.7641602071185019</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5702364997085813</v>
+        <v>0.7585169600094606</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5840662210446589</v>
+        <v>0.7544458960634532</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5601550995469635</v>
+        <v>0.7493070005265248</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5682285962062062</v>
+        <v>0.7371758142127892</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.557710067885088</v>
+        <v>0.7462485112301814</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5392296126523614</v>
+        <v>0.7787388887793918</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5392296126523614</v>
+        <v>0.7787388887793918</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5076430556454996</v>
+        <v>0.7716821902302913</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5141067099524438</v>
+        <v>0.7537437457589418</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5128424874492833</v>
+        <v>0.7544363932773772</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5143245701221143</v>
+        <v>0.7490810453909376</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5125869680903482</v>
+        <v>0.6949155167122332</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5125869680903482</v>
+        <v>0.6949155167122332</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.511954856838768</v>
+        <v>0.6959390019681326</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5101190593508823</v>
+        <v>0.5441485362893803</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5257159469420738</v>
+        <v>0.5438324806635901</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.530021060989585</v>
+        <v>0.5438324806635901</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5080734966592427</v>
+        <v>0.5389638865972705</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5083518930957683</v>
+        <v>0.5516719272213291</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5072006481604014</v>
+        <v>0.5493465602730045</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.51109819827176</v>
+        <v>0.5330017682221202</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5113765947082856</v>
+        <v>0.5302998093811504</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5172229198753234</v>
+        <v>0.52757497346259</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5128963365703811</v>
+        <v>0.5171518249572726</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5128963365703811</v>
+        <v>0.5082431389884531</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5128963365703811</v>
+        <v>0.494616495710372</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5057333475992443</v>
+        <v>0.494616495710372</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5054549511627187</v>
+        <v>0.497415242187302</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5040629689800906</v>
+        <v>0.497415242187302</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5025956684189335</v>
+        <v>0.4903852922212305</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5045821026638773</v>
+        <v>0.4912581407200718</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5055302695412477</v>
+        <v>0.4895648850233276</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5055302695412477</v>
+        <v>0.4895648850233276</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5055302695412477</v>
+        <v>0.4918902519716521</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5055302695412477</v>
+        <v>0.483929732880203</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5066061960980857</v>
+        <v>0.4823723318288429</v>
       </c>
     </row>
     <row r="151">
@@ -1930,57 +1930,57 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5025055679287305</v>
+        <v>0.4878420651032355</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.510202472695328</v>
+        <v>0.4878420651032355</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.510127154316799</v>
+        <v>0.4894747845331246</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5216878215109289</v>
+        <v>0.4856148936110306</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.556279370648076</v>
+        <v>0.490948772240039</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5121157002919818</v>
+        <v>0.4990222688992818</v>
       </c>
     </row>
   </sheetData>
